--- a/PinesSTM32F767ZI.xlsx
+++ b/PinesSTM32F767ZI.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tato2\Documents\Universidad\Sistemas-Embebidos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF7D2AB2-7AC7-4ED8-876C-BD5C413884FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB0AD728-5FE2-4B1E-9D0F-BF4082197E56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="18240" xr2:uid="{49454AD3-3FE9-40FF-965D-2DBDBD7E2F00}"/>
+    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="13185" xr2:uid="{49454AD3-3FE9-40FF-965D-2DBDBD7E2F00}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="17">
   <si>
     <t>Pines</t>
   </si>
@@ -81,6 +81,13 @@
   </si>
   <si>
     <t>Ubicación</t>
+  </si>
+  <si>
+    <t>8 (H)</t>
+  </si>
+  <si>
+    <t>A ~ G (16)
+H</t>
   </si>
 </sst>
 </file>
@@ -116,7 +123,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -124,6 +131,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -466,24 +474,26 @@
     <col min="3" max="3" width="4" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.28515625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="3"/>
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="1"/>
-      <c r="D1" t="s">
+      <c r="D1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="3" t="s">
         <v>14</v>
       </c>
     </row>
@@ -491,82 +501,119 @@
       <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="3">
         <v>20</v>
       </c>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="2"/>
-      <c r="B3" t="s">
+      <c r="B3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="3">
         <v>16</v>
       </c>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>
-      <c r="B4" t="s">
+      <c r="B4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="3">
         <v>30</v>
       </c>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
-      <c r="B5" t="s">
+      <c r="B5" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="3">
         <v>34</v>
       </c>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
-      <c r="B6" t="s">
+      <c r="B6" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="3">
         <f>SUM(C2:C5)</f>
         <v>100</v>
       </c>
+      <c r="D6" s="3">
+        <v>64</v>
+      </c>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="3">
         <v>70</v>
       </c>
-      <c r="D7" t="s">
-        <v>11</v>
-      </c>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
-      <c r="B8" t="s">
+      <c r="B8" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="3">
         <v>70</v>
       </c>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
-      <c r="B9" t="s">
+      <c r="B9" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="3">
         <f>SUM(C7:C8)</f>
         <v>140</v>
       </c>
+      <c r="D9" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G9" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="3">
